--- a/Dashboards/data/Data final/empleo/empleo adecuado/empleo_series.xlsx
+++ b/Dashboards/data/Data final/empleo/empleo adecuado/empleo_series.xlsx
@@ -560,7 +560,7 @@
         <v>2</v>
       </c>
       <c r="C44" s="1">
-        <v>4.6800436973571777</v>
+        <v>4.146550178527832</v>
       </c>
     </row>
     <row r="45">
@@ -571,7 +571,7 @@
         <v>3</v>
       </c>
       <c r="C45" s="1">
-        <v>33.683444976806641</v>
+        <v>33.940853118896484</v>
       </c>
     </row>
     <row r="46">
@@ -582,7 +582,7 @@
         <v>4</v>
       </c>
       <c r="C46" s="1">
-        <v>61.636512756347656</v>
+        <v>61.91259765625</v>
       </c>
     </row>
     <row r="47">
@@ -593,7 +593,7 @@
         <v>2</v>
       </c>
       <c r="C47" s="1">
-        <v>3.7986435890197754</v>
+        <v>3.1939144134521484</v>
       </c>
     </row>
     <row r="48">
@@ -604,7 +604,7 @@
         <v>3</v>
       </c>
       <c r="C48" s="1">
-        <v>35.495452880859375</v>
+        <v>36.035636901855469</v>
       </c>
     </row>
     <row r="49">
@@ -615,7 +615,7 @@
         <v>4</v>
       </c>
       <c r="C49" s="1">
-        <v>60.705902099609375</v>
+        <v>60.770450592041016</v>
       </c>
     </row>
     <row r="50">
@@ -626,7 +626,7 @@
         <v>2</v>
       </c>
       <c r="C50" s="1">
-        <v>3.5682029724121094</v>
+        <v>3.3833415508270264</v>
       </c>
     </row>
     <row r="51">
@@ -637,7 +637,7 @@
         <v>3</v>
       </c>
       <c r="C51" s="1">
-        <v>36.006023406982422</v>
+        <v>35.916843414306641</v>
       </c>
     </row>
     <row r="52">
@@ -648,7 +648,7 @@
         <v>4</v>
       </c>
       <c r="C52" s="1">
-        <v>60.425773620605469</v>
+        <v>60.699813842773438</v>
       </c>
     </row>
     <row r="53">
@@ -659,7 +659,7 @@
         <v>2</v>
       </c>
       <c r="C53" s="1">
-        <v>3.3848421573638916</v>
+        <v>2.6882493495941162</v>
       </c>
     </row>
     <row r="54">
@@ -670,7 +670,7 @@
         <v>3</v>
       </c>
       <c r="C54" s="1">
-        <v>34.098876953125</v>
+        <v>33.029060363769531</v>
       </c>
     </row>
     <row r="55">
@@ -681,7 +681,7 @@
         <v>4</v>
       </c>
       <c r="C55" s="1">
-        <v>62.516281127929688</v>
+        <v>64.282691955566406</v>
       </c>
     </row>
     <row r="56">
@@ -692,7 +692,7 @@
         <v>2</v>
       </c>
       <c r="C56" s="1">
-        <v>3.0951061248779297</v>
+        <v>2.6120502948760986</v>
       </c>
     </row>
     <row r="57">
@@ -703,7 +703,7 @@
         <v>3</v>
       </c>
       <c r="C57" s="1">
-        <v>36.767078399658203</v>
+        <v>37.068805694580078</v>
       </c>
     </row>
     <row r="58">
@@ -714,7 +714,7 @@
         <v>4</v>
       </c>
       <c r="C58" s="1">
-        <v>60.137813568115234</v>
+        <v>60.319145202636719</v>
       </c>
     </row>
   </sheetData>

--- a/Dashboards/data/Data final/empleo/empleo adecuado/empleo_series.xlsx
+++ b/Dashboards/data/Data final/empleo/empleo adecuado/empleo_series.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="60" uniqueCount="6">
   <si>
     <t>anio</t>
   </si>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -362,7 +362,7 @@
         <v>2</v>
       </c>
       <c r="C26" s="1">
-        <v>4.7728347778320312</v>
+        <v>4.7728347778320313</v>
       </c>
     </row>
     <row r="27">
